--- a/survey_templates/036_volunteer_satisfaction_survey--survey_templates.xlsx
+++ b/survey_templates/036_volunteer_satisfaction_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -830,8 +830,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -859,12 +859,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_a_week'}</t>
+          <t>less_than_a_week</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Less than a week'}</t>
+          <t>Less than a week</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'1-2_weeks'}</t>
+          <t>1-2_weeks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': '1-2 weeks'}</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_2_weeks'}</t>
+          <t>more_than_2_weeks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'More than 2 weeks'}</t>
+          <t>More than 2 weeks</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'environment'}</t>
+          <t>environment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Environment'}</t>
+          <t>Environment</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'community'}</t>
+          <t>community</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Community'}</t>
+          <t>Community</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'education'}</t>
+          <t>education</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Education'}</t>
+          <t>Education</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'animal'}</t>
+          <t>animal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Animal'}</t>
+          <t>Animal</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
